--- a/data/cfallone.xlsx
+++ b/data/cfallone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{C713C37E-26ED-4463-8AEB-085935B27266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EB737E-0475-4033-A84A-9BCB5EFA55E2}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{C713C37E-26ED-4463-8AEB-085935B27266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A852E7-2779-4D4A-AD4F-692881B35BD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1EDC94F7-17AE-4677-BF33-AE18A12550A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E258B218-6F9F-4769-859E-ED59397E0961}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -2656,35 +2656,219 @@
         <v>15</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" ref="D48" si="90">+D47+K47+E47-F47</f>
+        <f t="shared" ref="D48:D52" si="90">+D47+K47+E47-F47</f>
         <v>5903.8990000000022</v>
+      </c>
+      <c r="G48" s="4">
+        <v>82.65</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="83"/>
-        <v>3982.1100000000006</v>
+        <v>4064.7600000000007</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8.2650000000000006</v>
       </c>
       <c r="J48" s="5">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8.2650000000000006</v>
       </c>
       <c r="K48" s="5">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>74.385000000000005</v>
       </c>
       <c r="L48" s="5">
         <f t="shared" si="87"/>
-        <v>3583.898999999999</v>
+        <v>3658.2839999999992</v>
       </c>
       <c r="M48" s="5">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>2.4795000000000003</v>
       </c>
       <c r="N48" s="6">
         <f t="shared" si="89"/>
+        <v>1.3999223225194058E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <v>45902</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" si="90"/>
+        <v>5978.2840000000024</v>
+      </c>
+      <c r="G49" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="H49" s="5">
+        <f t="shared" ref="H49:H52" si="91">+H48+G49</f>
+        <v>4202.26</v>
+      </c>
+      <c r="I49" s="5">
+        <f t="shared" ref="I49:I52" si="92">+G49*0.1</f>
+        <v>13.75</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" ref="J49:J52" si="93">+I49</f>
+        <v>13.75</v>
+      </c>
+      <c r="K49" s="5">
+        <f t="shared" ref="K49:K52" si="94">+G49-I49</f>
+        <v>123.75</v>
+      </c>
+      <c r="L49" s="5">
+        <f t="shared" ref="L49:L52" si="95">+L48+K49</f>
+        <v>3782.0339999999992</v>
+      </c>
+      <c r="M49" s="5">
+        <f t="shared" ref="M49:M52" si="96">+K49/30</f>
+        <v>4.125</v>
+      </c>
+      <c r="N49" s="6">
+        <f t="shared" ref="N49:N52" si="97">+G49/D49</f>
+        <v>2.2999911011253388E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>45932</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4">
+        <f t="shared" si="90"/>
+        <v>6102.0340000000024</v>
+      </c>
+      <c r="G50" s="4">
+        <v>128.13999999999999</v>
+      </c>
+      <c r="H50" s="5">
+        <f t="shared" si="91"/>
+        <v>4330.4000000000005</v>
+      </c>
+      <c r="I50" s="5">
+        <f t="shared" si="92"/>
+        <v>12.814</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="93"/>
+        <v>12.814</v>
+      </c>
+      <c r="K50" s="5">
+        <f t="shared" si="94"/>
+        <v>115.32599999999999</v>
+      </c>
+      <c r="L50" s="5">
+        <f t="shared" si="95"/>
+        <v>3897.3599999999992</v>
+      </c>
+      <c r="M50" s="5">
+        <f t="shared" si="96"/>
+        <v>3.8441999999999998</v>
+      </c>
+      <c r="N50" s="6">
+        <f t="shared" si="97"/>
+        <v>2.0999555230272388E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <v>45963</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="4">
+        <f t="shared" si="90"/>
+        <v>6217.3600000000024</v>
+      </c>
+      <c r="G51" s="4">
+        <v>223.82</v>
+      </c>
+      <c r="H51" s="5">
+        <f t="shared" si="91"/>
+        <v>4554.22</v>
+      </c>
+      <c r="I51" s="5">
+        <f t="shared" si="92"/>
+        <v>22.382000000000001</v>
+      </c>
+      <c r="J51" s="5">
+        <f t="shared" si="93"/>
+        <v>22.382000000000001</v>
+      </c>
+      <c r="K51" s="5">
+        <f t="shared" si="94"/>
+        <v>201.43799999999999</v>
+      </c>
+      <c r="L51" s="5">
+        <f t="shared" si="95"/>
+        <v>4098.7979999999989</v>
+      </c>
+      <c r="M51" s="5">
+        <f t="shared" si="96"/>
+        <v>6.7145999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <f t="shared" si="97"/>
+        <v>3.5999202233745496E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>45993</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="4">
+        <f t="shared" si="90"/>
+        <v>6418.7980000000025</v>
+      </c>
+      <c r="H52" s="5">
+        <f t="shared" si="91"/>
+        <v>4554.22</v>
+      </c>
+      <c r="I52" s="5">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <f t="shared" si="95"/>
+        <v>4098.7979999999989</v>
+      </c>
+      <c r="M52" s="5">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N52" s="6">
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
     </row>

--- a/data/cfallone.xlsx
+++ b/data/cfallone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC126B4D-77D7-4A88-9482-E7187E56DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{CC126B4D-77D7-4A88-9482-E7187E56DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13C45D62-B930-406F-8F67-3A171D1BB82E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1EDC94F7-17AE-4677-BF33-AE18A12550A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E258B218-6F9F-4769-859E-ED59397E0961}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -2981,33 +2981,174 @@
         <f t="shared" si="98"/>
         <v>6744.5980000000027</v>
       </c>
+      <c r="G55" s="4">
+        <v>86.25</v>
+      </c>
       <c r="H55" s="5">
         <f t="shared" si="99"/>
-        <v>4916.22</v>
+        <v>5002.47</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="J55" s="5">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="K55" s="5">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>77.625</v>
       </c>
       <c r="L55" s="5">
         <f t="shared" si="103"/>
-        <v>4424.597999999999</v>
+        <v>4502.222999999999</v>
       </c>
       <c r="M55" s="5">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2.5874999999999999</v>
       </c>
       <c r="N55" s="6">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1.2788011976399477E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="4">
+        <f t="shared" ref="D56:D58" si="106">+D55+K55+E55-F55</f>
+        <v>6822.2230000000027</v>
+      </c>
+      <c r="G56" s="4">
+        <v>45.99</v>
+      </c>
+      <c r="H56" s="5">
+        <f t="shared" ref="H56:H58" si="107">+H55+G56</f>
+        <v>5048.46</v>
+      </c>
+      <c r="I56" s="5">
+        <f t="shared" ref="I56:I58" si="108">+G56*0.1</f>
+        <v>4.5990000000000002</v>
+      </c>
+      <c r="J56" s="5">
+        <f t="shared" ref="J56:J58" si="109">+I56</f>
+        <v>4.5990000000000002</v>
+      </c>
+      <c r="K56" s="5">
+        <f t="shared" ref="K56:K58" si="110">+G56-I56</f>
+        <v>41.391000000000005</v>
+      </c>
+      <c r="L56" s="5">
+        <f t="shared" ref="L56:L58" si="111">+L55+K56</f>
+        <v>4543.6139999999987</v>
+      </c>
+      <c r="M56" s="5">
+        <f t="shared" ref="M56:M58" si="112">+K56/30</f>
+        <v>1.3797000000000001</v>
+      </c>
+      <c r="N56" s="6">
+        <f t="shared" ref="N56:N58" si="113">+G56/D56</f>
+        <v>6.7412044431851585E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="4">
+        <f t="shared" si="106"/>
+        <v>6863.6140000000023</v>
+      </c>
+      <c r="G57" s="4">
+        <v>163.13999999999999</v>
+      </c>
+      <c r="H57" s="5">
+        <f t="shared" si="107"/>
+        <v>5211.6000000000004</v>
+      </c>
+      <c r="I57" s="5">
+        <f t="shared" si="108"/>
+        <v>16.314</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="109"/>
+        <v>16.314</v>
+      </c>
+      <c r="K57" s="5">
+        <f t="shared" si="110"/>
+        <v>146.82599999999999</v>
+      </c>
+      <c r="L57" s="5">
+        <f t="shared" si="111"/>
+        <v>4690.4399999999987</v>
+      </c>
+      <c r="M57" s="5">
+        <f t="shared" si="112"/>
+        <v>4.8941999999999997</v>
+      </c>
+      <c r="N57" s="6">
+        <f t="shared" si="113"/>
+        <v>2.3768819167278337E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="4">
+        <f t="shared" si="106"/>
+        <v>7010.4400000000023</v>
+      </c>
+      <c r="G58" s="4">
+        <v>127.45</v>
+      </c>
+      <c r="H58" s="5">
+        <f t="shared" si="107"/>
+        <v>5339.05</v>
+      </c>
+      <c r="I58" s="5">
+        <f t="shared" si="108"/>
+        <v>12.745000000000001</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="109"/>
+        <v>12.745000000000001</v>
+      </c>
+      <c r="K58" s="5">
+        <f t="shared" si="110"/>
+        <v>114.705</v>
+      </c>
+      <c r="L58" s="5">
+        <f t="shared" si="111"/>
+        <v>4805.1449999999986</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" si="112"/>
+        <v>3.8235000000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <f t="shared" si="113"/>
+        <v>1.81800286429953E-2</v>
       </c>
     </row>
   </sheetData>
